--- a/output_phyto/phyto_Intermediate_pagani_2000.xlsx
+++ b/output_phyto/phyto_Intermediate_pagani_2000.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
   <si>
     <t>NA</t>
   </si>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">10.1029/1999PA000484</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_pagani_2000.xlsx</t>
+    <t xml:space="preserve">phytoplankton_pagani_2000_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1641,6 +1641,30 @@
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2000_56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2000_64</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1672,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1714,12 +1738,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1833,7 +1851,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1932,7 +1950,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2658,7 +2675,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2676,8 +2693,8 @@
       <c r="H5" t="n">
         <v>14.7345454545455</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.0743866484997414</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2768,7 +2785,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2786,8 +2803,8 @@
       <c r="H6" t="n">
         <v>14.940900621118</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.0753741022347998</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2878,7 +2895,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2896,8 +2913,8 @@
       <c r="H7" t="n">
         <v>15.0402173913043</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.0758491019080182</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2988,7 +3005,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -3006,8 +3023,8 @@
       <c r="H8" t="n">
         <v>15.6304658385093</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.078668753421909</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3098,7 +3115,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3116,8 +3133,8 @@
       <c r="H9" t="n">
         <v>15.7108074534161</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.0790521190200914</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3208,7 +3225,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3226,8 +3243,8 @@
       <c r="H10" t="n">
         <v>15.7915527950311</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.0794373087746613</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3318,7 +3335,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3336,8 +3353,8 @@
       <c r="H11" t="n">
         <v>15.8319254658385</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.0796298653640576</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3428,7 +3445,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3446,8 +3463,8 @@
       <c r="H12" t="n">
         <v>16.0337888198758</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.080592268157411</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3538,7 +3555,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3556,8 +3573,8 @@
       <c r="H13" t="n">
         <v>16.0660869565217</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.0807461941614472</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3648,7 +3665,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3666,8 +3683,8 @@
       <c r="H14" t="n">
         <v>16.13625</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.0810805210205712</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3758,7 +3775,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3776,8 +3793,8 @@
       <c r="H15" t="n">
         <v>16.19125</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.081342543325218</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3868,7 +3885,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3886,8 +3903,8 @@
       <c r="H16" t="n">
         <v>16.285</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.0817890660785673</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3978,7 +3995,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3996,8 +4013,8 @@
       <c r="H17" t="n">
         <v>16.34875</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.082092625454706</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -4088,7 +4105,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4106,8 +4123,8 @@
       <c r="H18" t="n">
         <v>16.406835443038</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.0823691584347347</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4198,7 +4215,7 @@
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4216,8 +4233,8 @@
       <c r="H19" t="n">
         <v>16.6783544303797</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.083661135623712</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4308,7 +4325,7 @@
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4326,8 +4343,8 @@
       <c r="H20" t="n">
         <v>17.4526086956522</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.0873393745723903</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4418,7 +4435,7 @@
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4436,8 +4453,8 @@
       <c r="H21" t="n">
         <v>17.7460869565217</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.0887313691123269</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4528,7 +4545,7 @@
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4546,8 +4563,8 @@
       <c r="H22" t="n">
         <v>17.9251086956522</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.0895798991350675</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4565,7 +4582,7 @@
         <v>-23.66</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4603,20 +4620,20 @@
       <c r="AA22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4638,7 +4655,7 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4656,8 +4673,8 @@
       <c r="H23" t="n">
         <v>18.2057142857143</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.0909090365415511</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4748,7 +4765,7 @@
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4766,8 +4783,8 @@
       <c r="H24" t="n">
         <v>18.3427338129496</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.0915576669517403</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4858,7 +4875,7 @@
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4876,8 +4893,8 @@
       <c r="H25" t="n">
         <v>18.3725179856115</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.0916986276009703</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4895,7 +4912,7 @@
         <v>-22.52</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4933,20 +4950,20 @@
       <c r="AA25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -4968,7 +4985,7 @@
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -4986,8 +5003,8 @@
       <c r="H26" t="n">
         <v>18.4372661870504</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.0920050229870412</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -5005,7 +5022,7 @@
         <v>-23.04</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -5043,20 +5060,20 @@
       <c r="AA26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -5078,7 +5095,7 @@
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5096,8 +5113,8 @@
       <c r="H27" t="n">
         <v>18.4897122302158</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.0922531623858773</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5188,7 +5205,7 @@
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5206,8 +5223,8 @@
       <c r="H28" t="n">
         <v>18.6127338129496</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.0928350749027835</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5225,7 +5242,7 @@
         <v>-24.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5263,20 +5280,20 @@
       <c r="AA28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5298,7 +5315,7 @@
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5316,8 +5333,8 @@
       <c r="H29" t="n">
         <v>18.7253956834532</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.0933678094829145</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5335,7 +5352,7 @@
         <v>-23.05</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5373,20 +5390,20 @@
       <c r="AA29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5408,7 +5425,7 @@
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5426,8 +5443,8 @@
       <c r="H30" t="n">
         <v>18.7953237410072</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.0936983887630143</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5445,7 +5462,7 @@
         <v>-24.335</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5483,20 +5500,20 @@
       <c r="AA30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5518,7 +5535,7 @@
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5536,8 +5553,8 @@
       <c r="H31" t="n">
         <v>18.874964028777</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.0940748042560333</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5555,7 +5572,7 @@
         <v>-23.08</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5593,20 +5610,20 @@
       <c r="AA31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5628,7 +5645,7 @@
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5646,8 +5663,8 @@
       <c r="H32" t="n">
         <v>19.0122302158273</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.0947233925564712</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5665,7 +5682,7 @@
         <v>-23.24</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5703,20 +5720,20 @@
       <c r="AA32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
@@ -5738,7 +5755,7 @@
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5756,8 +5773,8 @@
       <c r="H33" t="n">
         <v>19.0446043165468</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.0948763260824649</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5775,7 +5792,7 @@
         <v>-22.59</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5813,20 +5830,20 @@
       <c r="AA33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
@@ -5848,7 +5865,7 @@
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -5866,8 +5883,8 @@
       <c r="H34" t="n">
         <v>19.1834892086331</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.0955322584078486</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -5958,7 +5975,7 @@
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -5976,8 +5993,8 @@
       <c r="H35" t="n">
         <v>19.2156329113924</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.0956840331347809</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -5995,7 +6012,7 @@
         <v>-22.91</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -6033,20 +6050,20 @@
       <c r="AA35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
@@ -6068,7 +6085,7 @@
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6086,8 +6103,8 @@
       <c r="H36" t="n">
         <v>19.2419620253165</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.0958083429923343</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6105,7 +6122,7 @@
         <v>-22.62</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6143,20 +6160,20 @@
       <c r="AA36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
@@ -6178,7 +6195,7 @@
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6196,8 +6213,8 @@
       <c r="H37" t="n">
         <v>19.2680168776371</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.0959313492820528</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6215,7 +6232,7 @@
         <v>-22.48</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6253,20 +6270,20 @@
       <c r="AA37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="e">
         <v>#N/A</v>
@@ -6288,7 +6305,7 @@
       <c r="B38" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" t="s">
         <v>272</v>
       </c>
       <c r="D38" t="s">
@@ -6306,8 +6323,8 @@
       <c r="H38" t="n">
         <v>19.2927004219409</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.0960478736088231</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -6325,7 +6342,7 @@
         <v>-22.675</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -6363,20 +6380,20 @@
       <c r="AA38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB38" t="e">
-        <v>#N/A</v>
+      <c r="AB38" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF38" t="e">
-        <v>#N/A</v>
+      <c r="AD38" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG38" t="e">
         <v>#N/A</v>
@@ -6398,7 +6415,7 @@
       <c r="B39" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" t="s">
         <v>272</v>
       </c>
       <c r="D39" t="s">
@@ -6416,8 +6433,8 @@
       <c r="H39" t="n">
         <v>19.3149156118143</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.096152738900055</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -6435,7 +6452,7 @@
         <v>-23.18</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -6473,20 +6490,20 @@
       <c r="AA39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB39" t="e">
-        <v>#N/A</v>
+      <c r="AB39" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" t="e">
-        <v>#N/A</v>
+      <c r="AD39" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG39" t="e">
         <v>#N/A</v>
@@ -6508,7 +6525,7 @@
       <c r="B40" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" t="s">
         <v>272</v>
       </c>
       <c r="D40" t="s">
@@ -6526,8 +6543,8 @@
       <c r="H40" t="n">
         <v>19.3486497890295</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.0963119668427235</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -6545,7 +6562,7 @@
         <v>-22.29</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -6583,20 +6600,20 @@
       <c r="AA40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB40" t="e">
-        <v>#N/A</v>
+      <c r="AB40" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF40" t="e">
-        <v>#N/A</v>
+      <c r="AD40" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG40" t="e">
         <v>#N/A</v>
@@ -6618,7 +6635,7 @@
       <c r="B41" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" t="s">
         <v>272</v>
       </c>
       <c r="D41" t="s">
@@ -6636,8 +6653,8 @@
       <c r="H41" t="n">
         <v>19.3751160337553</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.0964368795105868</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -6655,7 +6672,7 @@
         <v>-22.335</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -6693,20 +6710,20 @@
       <c r="AA41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB41" t="e">
-        <v>#N/A</v>
+      <c r="AB41" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF41" t="e">
-        <v>#N/A</v>
+      <c r="AD41" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG41" t="e">
         <v>#N/A</v>
@@ -6728,7 +6745,7 @@
       <c r="B42" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" t="s">
         <v>272</v>
       </c>
       <c r="D42" t="s">
@@ -6746,8 +6763,8 @@
       <c r="H42" t="n">
         <v>19.5477637130802</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.0972515080156797</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -6765,7 +6782,7 @@
         <v>-21.735</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -6803,20 +6820,20 @@
       <c r="AA42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB42" t="e">
-        <v>#N/A</v>
+      <c r="AB42" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF42" t="e">
-        <v>#N/A</v>
+      <c r="AD42" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG42" t="e">
         <v>#N/A</v>
@@ -6838,7 +6855,7 @@
       <c r="B43" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" t="s">
         <v>272</v>
       </c>
       <c r="D43" t="s">
@@ -6856,8 +6873,8 @@
       <c r="H43" t="n">
         <v>19.6026160337553</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.0975102474876191</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -6875,7 +6892,7 @@
         <v>-22.675</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -6913,20 +6930,20 @@
       <c r="AA43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB43" t="e">
-        <v>#N/A</v>
+      <c r="AB43" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF43" t="e">
-        <v>#N/A</v>
+      <c r="AD43" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG43" t="e">
         <v>#N/A</v>
@@ -6948,7 +6965,7 @@
       <c r="B44" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" t="s">
         <v>272</v>
       </c>
       <c r="D44" t="s">
@@ -6966,8 +6983,8 @@
       <c r="H44" t="n">
         <v>19.6300421940928</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.0976396031538309</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -6985,7 +7002,7 @@
         <v>-22.675</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -7023,20 +7040,20 @@
       <c r="AA44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB44" t="e">
-        <v>#N/A</v>
+      <c r="AB44" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF44" t="e">
-        <v>#N/A</v>
+      <c r="AD44" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG44" t="e">
         <v>#N/A</v>
@@ -7058,7 +7075,7 @@
       <c r="B45" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" t="s">
         <v>272</v>
       </c>
       <c r="D45" t="s">
@@ -7076,8 +7093,8 @@
       <c r="H45" t="n">
         <v>19.6979219409283</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.0979597181995518</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -7168,7 +7185,7 @@
       <c r="B46" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" t="s">
         <v>272</v>
       </c>
       <c r="D46" t="s">
@@ -7186,8 +7203,8 @@
       <c r="H46" t="n">
         <v>19.8031012658228</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.0984556220629406</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -7205,7 +7222,7 @@
         <v>-23.3</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -7243,20 +7260,20 @@
       <c r="AA46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB46" t="e">
-        <v>#N/A</v>
+      <c r="AB46" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF46" t="e">
-        <v>#N/A</v>
+      <c r="AD46" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG46" t="e">
         <v>#N/A</v>
@@ -7278,7 +7295,7 @@
       <c r="B47" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" t="s">
         <v>272</v>
       </c>
       <c r="D47" t="s">
@@ -7296,8 +7313,8 @@
       <c r="H47" t="n">
         <v>19.9163713080169</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.0989895198387285</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -7315,7 +7332,7 @@
         <v>-21.54</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -7353,20 +7370,20 @@
       <c r="AA47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB47" t="e">
-        <v>#N/A</v>
+      <c r="AB47" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF47" t="e">
-        <v>#N/A</v>
+      <c r="AD47" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG47" t="e">
         <v>#N/A</v>
@@ -7388,7 +7405,7 @@
       <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
       <c r="D48" t="s">
@@ -7406,8 +7423,8 @@
       <c r="H48" t="n">
         <v>19.9372151898734</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.0990877502108496</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -7425,7 +7442,7 @@
         <v>-23.56</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -7463,20 +7480,20 @@
       <c r="AA48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB48" t="e">
-        <v>#N/A</v>
+      <c r="AB48" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF48" t="e">
-        <v>#N/A</v>
+      <c r="AD48" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG48" t="e">
         <v>#N/A</v>
@@ -7498,7 +7515,7 @@
       <c r="B49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" t="s">
         <v>272</v>
       </c>
       <c r="D49" t="s">
@@ -7516,8 +7533,8 @@
       <c r="H49" t="n">
         <v>20.0386919831224</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.0995659011397974</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -7535,7 +7552,7 @@
         <v>-22.79</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -7573,20 +7590,20 @@
       <c r="AA49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB49" t="e">
-        <v>#N/A</v>
+      <c r="AB49" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF49" t="e">
-        <v>#N/A</v>
+      <c r="AD49" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG49" t="e">
         <v>#N/A</v>
@@ -7608,7 +7625,7 @@
       <c r="B50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="34" t="s">
+      <c r="C50" t="s">
         <v>272</v>
       </c>
       <c r="D50" t="s">
@@ -7626,8 +7643,8 @@
       <c r="H50" t="n">
         <v>20.0587130801688</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.0996602241921162</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -7645,7 +7662,7 @@
         <v>-22.535</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -7683,20 +7700,20 @@
       <c r="AA50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB50" t="e">
-        <v>#N/A</v>
+      <c r="AB50" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF50" t="e">
-        <v>#N/A</v>
+      <c r="AD50" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG50" t="e">
         <v>#N/A</v>
@@ -7718,7 +7735,7 @@
       <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C51" t="s">
         <v>272</v>
       </c>
       <c r="D51" t="s">
@@ -7736,8 +7753,8 @@
       <c r="H51" t="n">
         <v>20.1571729957806</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.100124016009458</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -7755,7 +7772,7 @@
         <v>-23.245</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -7793,20 +7810,20 @@
       <c r="AA51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB51" t="e">
-        <v>#N/A</v>
+      <c r="AB51" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF51" t="e">
-        <v>#N/A</v>
+      <c r="AD51" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG51" t="e">
         <v>#N/A</v>
@@ -7828,7 +7845,7 @@
       <c r="B52" t="s">
         <v>271</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" t="s">
         <v>272</v>
       </c>
       <c r="D52" t="s">
@@ -7846,8 +7863,8 @@
       <c r="H52" t="n">
         <v>20.2675632911392</v>
       </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+      <c r="I52" t="n">
+        <v>0.100643865948228</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -7865,7 +7882,7 @@
         <v>-25.13</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P52" t="e">
         <v>#N/A</v>
@@ -7903,20 +7920,20 @@
       <c r="AA52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB52" t="e">
-        <v>#N/A</v>
+      <c r="AB52" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF52" t="e">
-        <v>#N/A</v>
+      <c r="AD52" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG52" t="e">
         <v>#N/A</v>
@@ -7938,7 +7955,7 @@
       <c r="B53" t="s">
         <v>271</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" t="s">
         <v>272</v>
       </c>
       <c r="D53" t="s">
@@ -7956,8 +7973,8 @@
       <c r="H53" t="n">
         <v>20.3993459915612</v>
       </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+      <c r="I53" t="n">
+        <v>0.101264265033395</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -7975,7 +7992,7 @@
         <v>-27.22</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P53" t="e">
         <v>#N/A</v>
@@ -8013,20 +8030,20 @@
       <c r="AA53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB53" t="e">
-        <v>#N/A</v>
+      <c r="AB53" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF53" t="e">
-        <v>#N/A</v>
+      <c r="AD53" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG53" t="e">
         <v>#N/A</v>
@@ -8048,7 +8065,7 @@
       <c r="B54" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" t="s">
         <v>272</v>
       </c>
       <c r="D54" t="s">
@@ -8066,8 +8083,8 @@
       <c r="H54" t="n">
         <v>20.4421308016878</v>
       </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+      <c r="I54" t="n">
+        <v>0.101465640220057</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -8085,7 +8102,7 @@
         <v>-26.61</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P54" t="e">
         <v>#N/A</v>
@@ -8123,20 +8140,20 @@
       <c r="AA54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB54" t="e">
-        <v>#N/A</v>
+      <c r="AB54" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF54" t="e">
-        <v>#N/A</v>
+      <c r="AD54" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG54" t="e">
         <v>#N/A</v>
@@ -8158,7 +8175,7 @@
       <c r="B55" t="s">
         <v>271</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" t="s">
         <v>272</v>
       </c>
       <c r="D55" t="s">
@@ -8176,8 +8193,8 @@
       <c r="H55" t="n">
         <v>20.497805907173</v>
       </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+      <c r="I55" t="n">
+        <v>0.101727653455334</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -8195,7 +8212,7 @@
         <v>-27.74</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P55" t="e">
         <v>#N/A</v>
@@ -8233,20 +8250,20 @@
       <c r="AA55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB55" t="e">
-        <v>#N/A</v>
+      <c r="AB55" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF55" t="e">
-        <v>#N/A</v>
+      <c r="AD55" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG55" t="e">
         <v>#N/A</v>
@@ -8268,7 +8285,7 @@
       <c r="B56" t="s">
         <v>271</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" t="s">
         <v>272</v>
       </c>
       <c r="D56" t="s">
@@ -8286,8 +8303,8 @@
       <c r="H56" t="n">
         <v>20.750625</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="n">
+        <v>0.102916986016231</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -8305,7 +8322,7 @@
         <v>-25.475</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P56" t="e">
         <v>#N/A</v>
@@ -8343,20 +8360,20 @@
       <c r="AA56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB56" t="e">
-        <v>#N/A</v>
+      <c r="AB56" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF56" t="e">
-        <v>#N/A</v>
+      <c r="AD56" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG56" t="e">
         <v>#N/A</v>
@@ -8378,7 +8395,7 @@
       <c r="B57" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" t="s">
         <v>272</v>
       </c>
       <c r="D57" t="s">
@@ -8396,8 +8413,8 @@
       <c r="H57" t="n">
         <v>20.84375</v>
       </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+      <c r="I57" t="n">
+        <v>0.10335488275442</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -8415,7 +8432,7 @@
         <v>-26.63</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P57" t="e">
         <v>#N/A</v>
@@ -8453,20 +8470,20 @@
       <c r="AA57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB57" t="e">
-        <v>#N/A</v>
+      <c r="AB57" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF57" t="e">
-        <v>#N/A</v>
+      <c r="AD57" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG57" t="e">
         <v>#N/A</v>
@@ -8488,7 +8505,7 @@
       <c r="B58" t="s">
         <v>271</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" t="s">
         <v>272</v>
       </c>
       <c r="D58" t="s">
@@ -8506,8 +8523,8 @@
       <c r="H58" t="n">
         <v>21.49625</v>
       </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+      <c r="I58" t="n">
+        <v>0.106420282772272</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -8525,7 +8542,7 @@
         <v>-26.355</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P58" t="e">
         <v>#N/A</v>
@@ -8563,20 +8580,20 @@
       <c r="AA58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB58" t="e">
-        <v>#N/A</v>
+      <c r="AB58" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF58" t="e">
-        <v>#N/A</v>
+      <c r="AD58" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG58" t="e">
         <v>#N/A</v>
@@ -8598,7 +8615,7 @@
       <c r="B59" t="s">
         <v>271</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" t="s">
         <v>272</v>
       </c>
       <c r="D59" t="s">
@@ -8616,8 +8633,8 @@
       <c r="H59" t="n">
         <v>22.2373333333333</v>
       </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+      <c r="I59" t="n">
+        <v>0.109896007355835</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -8635,7 +8652,7 @@
         <v>-27.055</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P59" t="e">
         <v>#N/A</v>
@@ -8673,20 +8690,20 @@
       <c r="AA59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB59" t="e">
-        <v>#N/A</v>
+      <c r="AB59" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF59" t="e">
-        <v>#N/A</v>
+      <c r="AD59" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG59" t="e">
         <v>#N/A</v>
@@ -8708,7 +8725,7 @@
       <c r="B60" t="s">
         <v>271</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" t="s">
         <v>272</v>
       </c>
       <c r="D60" t="s">
@@ -8726,8 +8743,8 @@
       <c r="H60" t="n">
         <v>22.8593333333333</v>
       </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+      <c r="I60" t="n">
+        <v>0.112808587268652</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -8745,7 +8762,7 @@
         <v>-25.06</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P60" t="e">
         <v>#N/A</v>
@@ -8783,20 +8800,20 @@
       <c r="AA60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB60" t="e">
-        <v>#N/A</v>
+      <c r="AB60" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF60" t="e">
-        <v>#N/A</v>
+      <c r="AD60" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG60" t="e">
         <v>#N/A</v>
@@ -8812,36 +8829,884 @@
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="R61" s="11"/>
-      <c r="V61" s="11"/>
+      <c r="A61" t="s">
+        <v>333</v>
+      </c>
+      <c r="B61" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" t="s">
+        <v>272</v>
+      </c>
+      <c r="D61" t="s">
+        <v>273</v>
+      </c>
+      <c r="E61" t="s">
+        <v>274</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H61" t="n">
+        <v>23.535</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.115967821625875</v>
+      </c>
+      <c r="J61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L61" t="s">
+        <v>275</v>
+      </c>
+      <c r="M61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R61" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V61" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AG61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="62" ht="19" customHeight="1">
-      <c r="R62" s="11"/>
-      <c r="V62" s="11"/>
+      <c r="A62" t="s">
+        <v>334</v>
+      </c>
+      <c r="B62" t="s">
+        <v>271</v>
+      </c>
+      <c r="C62" t="s">
+        <v>272</v>
+      </c>
+      <c r="D62" t="s">
+        <v>273</v>
+      </c>
+      <c r="E62" t="s">
+        <v>274</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H62" t="n">
+        <v>23.8261375661376</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.117327646331029</v>
+      </c>
+      <c r="J62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L62" t="s">
+        <v>275</v>
+      </c>
+      <c r="M62" t="s">
+        <v>294</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-25.36</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.707106781186547</v>
+      </c>
+      <c r="P62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R62" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V62" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="63" ht="19" customHeight="1">
-      <c r="R63" s="11"/>
-      <c r="V63" s="11"/>
+      <c r="A63" t="s">
+        <v>335</v>
+      </c>
+      <c r="B63" t="s">
+        <v>271</v>
+      </c>
+      <c r="C63" t="s">
+        <v>272</v>
+      </c>
+      <c r="D63" t="s">
+        <v>273</v>
+      </c>
+      <c r="E63" t="s">
+        <v>274</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H63" t="n">
+        <v>23.8289021164021</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.117340554654803</v>
+      </c>
+      <c r="J63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L63" t="s">
+        <v>275</v>
+      </c>
+      <c r="M63" t="s">
+        <v>294</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-27.06</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.707106781186547</v>
+      </c>
+      <c r="P63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R63" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V63" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="64" ht="19" customHeight="1">
-      <c r="R64" s="11"/>
-      <c r="V64" s="11"/>
+      <c r="A64" t="s">
+        <v>336</v>
+      </c>
+      <c r="B64" t="s">
+        <v>271</v>
+      </c>
+      <c r="C64" t="s">
+        <v>272</v>
+      </c>
+      <c r="D64" t="s">
+        <v>273</v>
+      </c>
+      <c r="E64" t="s">
+        <v>274</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H64" t="n">
+        <v>24.3446164021164</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.119747196909406</v>
+      </c>
+      <c r="J64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L64" t="s">
+        <v>275</v>
+      </c>
+      <c r="M64" t="s">
+        <v>294</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.707106781186547</v>
+      </c>
+      <c r="P64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R64" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V64" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="65" ht="19" customHeight="1">
-      <c r="R65" s="11"/>
-      <c r="V65" s="11"/>
+      <c r="A65" t="s">
+        <v>337</v>
+      </c>
+      <c r="B65" t="s">
+        <v>271</v>
+      </c>
+      <c r="C65" t="s">
+        <v>272</v>
+      </c>
+      <c r="D65" t="s">
+        <v>273</v>
+      </c>
+      <c r="E65" t="s">
+        <v>274</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H65" t="n">
+        <v>24.5089814814815</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.120513668662012</v>
+      </c>
+      <c r="J65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L65" t="s">
+        <v>275</v>
+      </c>
+      <c r="M65" t="s">
+        <v>294</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-27.465</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.707106781186547</v>
+      </c>
+      <c r="P65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R65" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V65" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="66" ht="19" customHeight="1">
-      <c r="R66" s="11"/>
-      <c r="V66" s="11"/>
+      <c r="A66" t="s">
+        <v>338</v>
+      </c>
+      <c r="B66" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" t="s">
+        <v>272</v>
+      </c>
+      <c r="D66" t="s">
+        <v>273</v>
+      </c>
+      <c r="E66" t="s">
+        <v>274</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H66" t="n">
+        <v>24.5765873015873</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.120828852603182</v>
+      </c>
+      <c r="J66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L66" t="s">
+        <v>275</v>
+      </c>
+      <c r="M66" t="s">
+        <v>294</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-27.78</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.707106781186547</v>
+      </c>
+      <c r="P66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R66" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V66" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="67" ht="19" customHeight="1">
-      <c r="R67" s="11"/>
-      <c r="V67" s="11"/>
+      <c r="A67" t="s">
+        <v>339</v>
+      </c>
+      <c r="B67" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" t="s">
+        <v>272</v>
+      </c>
+      <c r="D67" t="s">
+        <v>273</v>
+      </c>
+      <c r="E67" t="s">
+        <v>274</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H67" t="n">
+        <v>24.6517328042328</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.121179134475381</v>
+      </c>
+      <c r="J67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L67" t="s">
+        <v>275</v>
+      </c>
+      <c r="M67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R67" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V67" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AG67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="68" ht="19" customHeight="1">
-      <c r="R68" s="11"/>
-      <c r="V68" s="11"/>
+      <c r="A68" t="s">
+        <v>340</v>
+      </c>
+      <c r="B68" t="s">
+        <v>271</v>
+      </c>
+      <c r="C68" t="s">
+        <v>272</v>
+      </c>
+      <c r="D68" t="s">
+        <v>273</v>
+      </c>
+      <c r="E68" t="s">
+        <v>274</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-30.2765</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-35.285</v>
+      </c>
+      <c r="H68" t="n">
+        <v>25.02421875</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.122914620565023</v>
+      </c>
+      <c r="J68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L68" t="s">
+        <v>275</v>
+      </c>
+      <c r="M68" t="s">
+        <v>294</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-28.985</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.707106781186547</v>
+      </c>
+      <c r="P68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R68" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V68" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="R69" s="11"/>
@@ -9001,64 +9866,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
